--- a/requirement/requirement.xlsx
+++ b/requirement/requirement.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dhruv\School management\school-management\requirement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Dhruv code\schoolManagement\requirement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73C689C-F3B1-4567-B08C-B86FD39EB745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA58778E-A1AB-4459-A6C2-0BD1C58F4883}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirement" sheetId="1" r:id="rId1"/>
     <sheet name="Admin Modules" sheetId="2" r:id="rId2"/>
     <sheet name="Branches" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="143">
   <si>
     <t>Requiremenmts</t>
   </si>
@@ -776,6 +777,9 @@
   </si>
   <si>
     <t>1.8.3 Expenses</t>
+  </si>
+  <si>
+    <t>Dashboard</t>
   </si>
 </sst>
 </file>
@@ -1112,18 +1116,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="33.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1132,12 +1136,12 @@
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1160,12 +1164,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -1194,12 +1198,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -1233,19 +1237,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FF89778-C23C-4F4F-8031-DAA6A5F6FE5E}">
   <dimension ref="A1:C75"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="56" customWidth="1"/>
-    <col min="3" max="3" width="44.44140625" customWidth="1"/>
+    <col min="3" max="3" width="44.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="4"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -1253,7 +1257,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1261,57 +1265,57 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -1319,140 +1323,140 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C19" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C27" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B33" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C35" s="1"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C37" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C38" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C46" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>3</v>
       </c>
@@ -1460,87 +1464,87 @@
         <v>55</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C51" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B65" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>4</v>
       </c>
@@ -1548,32 +1552,32 @@
         <v>72</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B70" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
         <v>78</v>
       </c>
@@ -1590,32 +1594,32 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CA302E6-A7D2-4147-907D-75705999803A}">
   <dimension ref="A1:U11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>85</v>
       </c>
@@ -1680,7 +1684,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>90</v>
       </c>
@@ -1700,7 +1704,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>98</v>
       </c>
@@ -1720,7 +1724,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>99</v>
       </c>
@@ -1737,7 +1741,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>100</v>
       </c>
@@ -1751,7 +1755,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>101</v>
       </c>
@@ -1762,7 +1766,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>102</v>
       </c>
@@ -1773,7 +1777,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>103</v>
       </c>
@@ -1784,7 +1788,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>123</v>
       </c>
@@ -1795,7 +1799,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>126</v>
       </c>
@@ -1803,9 +1807,369 @@
         <v>138</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>129</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1FDB72D-CAF0-4F13-848C-00EE3D45606E}">
+  <dimension ref="A1:C71"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C38" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C39" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C40" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C41" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C45" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C46" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C47" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C49" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C51" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C55" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C57" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C59" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C61" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C63" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C65" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C67" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C69" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B70" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C71" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/requirement/requirement.xlsx
+++ b/requirement/requirement.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Dhruv code\schoolManagement\requirement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dhruv\School management\school-management\requirement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA58778E-A1AB-4459-A6C2-0BD1C58F4883}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6FECC57-52F7-4CA9-BC4C-161679C88911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirement" sheetId="1" r:id="rId1"/>
     <sheet name="Admin Modules" sheetId="2" r:id="rId2"/>
-    <sheet name="Branches" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
+    <sheet name="Attendance" sheetId="6" r:id="rId3"/>
+    <sheet name="Branches" sheetId="3" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId5"/>
+    <sheet name="Time Table" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="197">
   <si>
     <t>Requiremenmts</t>
   </si>
@@ -780,6 +782,247 @@
   </si>
   <si>
     <t>Dashboard</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Add Time Table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fields: </t>
+  </si>
+  <si>
+    <t>1. Teacher Name(Dropdown)</t>
+  </si>
+  <si>
+    <t>2. Class(Dropdown)</t>
+  </si>
+  <si>
+    <t>3. Section(Dropdown)</t>
+  </si>
+  <si>
+    <t>4. Day selection</t>
+  </si>
+  <si>
+    <t>Desc: In day selection there is a (+) add row button which include various fields</t>
+  </si>
+  <si>
+    <t>Coloumn : Day, Start Time, End Time</t>
+  </si>
+  <si>
+    <t>Example: Monday, 8:00 AM, 8:45 AM</t>
+  </si>
+  <si>
+    <t>Options: Regular Time Table, Subsitution(Replacement)</t>
+  </si>
+  <si>
+    <t>For Regular Time Table</t>
+  </si>
+  <si>
+    <t>Subsitution</t>
+  </si>
+  <si>
+    <t>1. Unavailable Teacher Name(Dropdown)</t>
+  </si>
+  <si>
+    <t>2. Replacement Teacher(Dropdown)</t>
+  </si>
+  <si>
+    <t>4. Section(dropdown)</t>
+  </si>
+  <si>
+    <t>3. Class(dropdown)</t>
+  </si>
+  <si>
+    <t>5. Date</t>
+  </si>
+  <si>
+    <t>Desc: According to date we need to reflect completed time table of that particular day as a list on the basis of time assigned earlier, with checkbox</t>
+  </si>
+  <si>
+    <t>6. Submit Button</t>
+  </si>
+  <si>
+    <t>5. Submitt Button</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>View Mode Time table</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Fields: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Weekly time table, date wise time table, today time table, tomorrow time table</t>
+    </r>
+  </si>
+  <si>
+    <t>Parents</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Admin Has Option </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Manage Attendance</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Students Attendance</t>
+  </si>
+  <si>
+    <t>2. Staff Attendance</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">By Clicking on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Students Attendance</t>
+    </r>
+  </si>
+  <si>
+    <t>There is some filter on that basis lost will reflect</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Filters</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Type(Dropdown), Class(Dropdown), Section(Dropdown), Date---&gt; Search Button</t>
+    </r>
+  </si>
+  <si>
+    <t>Type: Manual Attendance, Digital Attendance</t>
+  </si>
+  <si>
+    <t>Class: All Class</t>
+  </si>
+  <si>
+    <t>Section: Respected section list on basis of class selection</t>
+  </si>
+  <si>
+    <t>Date: ccalendar(by default today date)</t>
+  </si>
+  <si>
+    <t>By clicking on search button we got some information with list of the students of class</t>
+  </si>
+  <si>
+    <t>It has one information ticket, which has basic information of selected class by filter(Refer screenshot)</t>
+  </si>
+  <si>
+    <t>List of students</t>
+  </si>
+  <si>
+    <t>S.No., Roll number, Name, Parent Name, Class, Attendance status(dropdown)</t>
+  </si>
+  <si>
+    <t>There is few selection options also above the student list, so we can select from that also</t>
+  </si>
+  <si>
+    <t>Attendance status: Present, Absent, Holiday, Saturday, Sunday, On Leave</t>
+  </si>
+  <si>
+    <t>Mark All Present, Mark All Absent, Mark All Holiday, Mark All Sunday, Mark All Saturday</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In Below we have option </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Notify to Parents(Yes/No)</t>
+    </r>
+  </si>
+  <si>
+    <t>Teachers</t>
+  </si>
+  <si>
+    <t>Same as Admin functionality</t>
+  </si>
+  <si>
+    <t>Parents and Students</t>
+  </si>
+  <si>
+    <t>View Functionality</t>
+  </si>
+  <si>
+    <t>In view functionality, we have monthly calendar, and we will show attendance status by there colour code</t>
+  </si>
+  <si>
+    <t>Green: Present</t>
+  </si>
+  <si>
+    <t>Absent: Red</t>
+  </si>
+  <si>
+    <t>Holiday: Purple</t>
+  </si>
+  <si>
+    <t>On Leave: Light Blue</t>
+  </si>
+  <si>
+    <t>View changes on the selection basis</t>
+  </si>
+  <si>
+    <t>Current Month, Today, Year Basis, Date selection basis</t>
   </si>
 </sst>
 </file>
@@ -1116,18 +1359,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1136,12 +1379,12 @@
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1164,12 +1407,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -1198,12 +1441,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -1237,19 +1480,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FF89778-C23C-4F4F-8031-DAA6A5F6FE5E}">
   <dimension ref="A1:C75"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="56" customWidth="1"/>
-    <col min="3" max="3" width="44.42578125" customWidth="1"/>
+    <col min="3" max="3" width="44.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="4"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -1257,7 +1500,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1265,57 +1508,57 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -1323,140 +1566,140 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C19" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C27" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C34" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C35" s="1"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C37" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C38" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C39" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C40" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C43" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C44" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C45" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C46" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>3</v>
       </c>
@@ -1464,87 +1707,87 @@
         <v>55</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C51" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>4</v>
       </c>
@@ -1552,32 +1795,32 @@
         <v>72</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B72" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B74" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
         <v>78</v>
       </c>
@@ -1592,224 +1835,158 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CA302E6-A7D2-4147-907D-75705999803A}">
-  <dimension ref="A1:U11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E545D5B-ADC3-4BF1-B47C-66D098836D2D}">
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G1" t="s">
-        <v>108</v>
-      </c>
-      <c r="H1" t="s">
-        <v>109</v>
-      </c>
-      <c r="I1" t="s">
-        <v>110</v>
-      </c>
-      <c r="J1" t="s">
-        <v>111</v>
-      </c>
-      <c r="K1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L1" t="s">
-        <v>113</v>
-      </c>
-      <c r="M1" t="s">
-        <v>114</v>
-      </c>
-      <c r="N1" t="s">
-        <v>115</v>
-      </c>
-      <c r="O1" t="s">
-        <v>116</v>
-      </c>
-      <c r="P1" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>118</v>
-      </c>
-      <c r="R1" t="s">
-        <v>119</v>
-      </c>
-      <c r="S1" t="s">
-        <v>120</v>
-      </c>
-      <c r="T1" t="s">
-        <v>124</v>
-      </c>
-      <c r="U1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>98</v>
-      </c>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" t="s">
-        <v>133</v>
-      </c>
-      <c r="G3" t="s">
-        <v>135</v>
-      </c>
-      <c r="I3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>99</v>
-      </c>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" t="s">
-        <v>104</v>
-      </c>
-      <c r="G4" t="s">
-        <v>136</v>
-      </c>
-      <c r="I4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C5" t="s">
-        <v>96</v>
-      </c>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
-        <v>105</v>
-      </c>
-      <c r="G5" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" t="s">
-        <v>121</v>
-      </c>
-      <c r="D7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" t="s">
-        <v>130</v>
-      </c>
-      <c r="D8" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>123</v>
-      </c>
-      <c r="C9" t="s">
-        <v>131</v>
-      </c>
-      <c r="D9" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>126</v>
-      </c>
-      <c r="D10" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>129</v>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F11" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D16" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E18" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E20" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C31" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D32" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D33" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D34" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="35" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D35" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="37" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C37" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="38" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D38" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -1818,361 +1995,741 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1FDB72D-CAF0-4F13-848C-00EE3D45606E}">
-  <dimension ref="A1:C71"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CA302E6-A7D2-4147-907D-75705999803A}">
+  <dimension ref="A1:U11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J1" t="s">
+        <v>111</v>
+      </c>
+      <c r="K1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M1" t="s">
+        <v>114</v>
+      </c>
+      <c r="N1" t="s">
+        <v>115</v>
+      </c>
+      <c r="O1" t="s">
+        <v>116</v>
+      </c>
+      <c r="P1" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>118</v>
+      </c>
+      <c r="R1" t="s">
+        <v>119</v>
+      </c>
+      <c r="S1" t="s">
+        <v>120</v>
+      </c>
+      <c r="T1" t="s">
+        <v>124</v>
+      </c>
+      <c r="U1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="C2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>98</v>
+      </c>
       <c r="C3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+      <c r="D3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G3" t="s">
+        <v>135</v>
+      </c>
+      <c r="I3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>99</v>
+      </c>
       <c r="C4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="D4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G4" t="s">
+        <v>136</v>
+      </c>
+      <c r="I4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>100</v>
+      </c>
       <c r="C5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+      <c r="D5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>101</v>
+      </c>
       <c r="C6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+      <c r="D6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>102</v>
+      </c>
       <c r="C7" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+      <c r="D7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>103</v>
+      </c>
       <c r="C8" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+      <c r="D8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>123</v>
+      </c>
       <c r="C9" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C10" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
+        <v>131</v>
+      </c>
+      <c r="D9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C12" t="s">
+      <c r="D10" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
         <v>129</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C14" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C15" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C16" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C18" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C19" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C20" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C21" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C23" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C24" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C25" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C26" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C27" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C28" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C29" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C30" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C31" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C33" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C34" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C38" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C39" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C40" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C41" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B42" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B44" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C45" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C46" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C47" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B48" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C49" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B50" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C51" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B52" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C53" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B54" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C55" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B56" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C57" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B58" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C59" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B60" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C61" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B62" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C63" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B64" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C65" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B66" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C67" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B68" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C69" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B70" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C71" t="s">
-        <v>142</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1FDB72D-CAF0-4F13-848C-00EE3D45606E}">
+  <dimension ref="A1:C71"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C11" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C21" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C23" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C24" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C26" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C28" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C29" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C30" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C31" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C33" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C34" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C38" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C39" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C40" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C41" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B42" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B44" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C45" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C46" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C47" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B48" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C49" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B50" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C51" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B52" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B54" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C55" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B56" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C57" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B58" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C59" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B60" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C61" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B62" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C63" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B64" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C65" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B66" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C67" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B68" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C69" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B70" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C71" t="s">
+        <v>142</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E73829DA-9CC1-427E-AD47-A7113729ECA5}">
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C4" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C5" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E10" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E12" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C15" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D20" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D21" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C28" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C34" t="s">
+        <v>166</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>